--- a/FastTest PlugIn - Formula.xlsx
+++ b/FastTest PlugIn - Formula.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mi unidad\FTP\z. V8.0\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4734179-7E05-4920-A1A9-28C7F7BBD236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496915DE-200A-4A5C-AC3A-FEEB73AD1221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12266" tabRatio="805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" tabRatio="805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Formulas DG" sheetId="9" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="191">
   <si>
     <t>DATO_01</t>
   </si>
@@ -229,78 +229,6 @@
     <t>RETROALIM. C</t>
   </si>
   <si>
-    <t>P09_1</t>
-  </si>
-  <si>
-    <t>P01_1</t>
-  </si>
-  <si>
-    <t>P01_2</t>
-  </si>
-  <si>
-    <t>P02_1</t>
-  </si>
-  <si>
-    <t>P02_2</t>
-  </si>
-  <si>
-    <t>P03_1</t>
-  </si>
-  <si>
-    <t>P03_2</t>
-  </si>
-  <si>
-    <t>P04_1</t>
-  </si>
-  <si>
-    <t>P04_2</t>
-  </si>
-  <si>
-    <t>P05_1</t>
-  </si>
-  <si>
-    <t>P05_2</t>
-  </si>
-  <si>
-    <t>P06_1</t>
-  </si>
-  <si>
-    <t>P06_2</t>
-  </si>
-  <si>
-    <t>P07_1</t>
-  </si>
-  <si>
-    <t>P07_2</t>
-  </si>
-  <si>
-    <t>P08_1</t>
-  </si>
-  <si>
-    <t>P08_2</t>
-  </si>
-  <si>
-    <t>P09_2</t>
-  </si>
-  <si>
-    <t>P10_1</t>
-  </si>
-  <si>
-    <t>P10_2</t>
-  </si>
-  <si>
-    <t>P11_1</t>
-  </si>
-  <si>
-    <t>P11_2</t>
-  </si>
-  <si>
-    <t>P12_1</t>
-  </si>
-  <si>
-    <t>P12_2</t>
-  </si>
-  <si>
     <t>Editor HTML</t>
   </si>
   <si>
@@ -544,7 +472,151 @@
     <t>SubCat_12</t>
   </si>
   <si>
-    <t>V - 8.0</t>
+    <t>P_01_1</t>
+  </si>
+  <si>
+    <t>P_01_2</t>
+  </si>
+  <si>
+    <t>P_02_1</t>
+  </si>
+  <si>
+    <t>P_02_2</t>
+  </si>
+  <si>
+    <t>P_03_1</t>
+  </si>
+  <si>
+    <t>P_03_2</t>
+  </si>
+  <si>
+    <t>P_04_1</t>
+  </si>
+  <si>
+    <t>P_04_2</t>
+  </si>
+  <si>
+    <t>P_05_1</t>
+  </si>
+  <si>
+    <t>P_05_2</t>
+  </si>
+  <si>
+    <t>P_06_1</t>
+  </si>
+  <si>
+    <t>P_06_2</t>
+  </si>
+  <si>
+    <t>P_07_1</t>
+  </si>
+  <si>
+    <t>P_07_2</t>
+  </si>
+  <si>
+    <t>P_08_1</t>
+  </si>
+  <si>
+    <t>P_08_2</t>
+  </si>
+  <si>
+    <t>P_09_1</t>
+  </si>
+  <si>
+    <t>P_09_2</t>
+  </si>
+  <si>
+    <t>P_10_1</t>
+  </si>
+  <si>
+    <t>P_10_2</t>
+  </si>
+  <si>
+    <t>P_11_1</t>
+  </si>
+  <si>
+    <t>P_11_2</t>
+  </si>
+  <si>
+    <t>P_12_1</t>
+  </si>
+  <si>
+    <t>P_12_2</t>
+  </si>
+  <si>
+    <t>V - 8.3</t>
+  </si>
+  <si>
+    <t>PP_01_1</t>
+  </si>
+  <si>
+    <t>PP_01_2</t>
+  </si>
+  <si>
+    <t>PP_02_1</t>
+  </si>
+  <si>
+    <t>PP_02_2</t>
+  </si>
+  <si>
+    <t>PP_03_1</t>
+  </si>
+  <si>
+    <t>PP_03_2</t>
+  </si>
+  <si>
+    <t>PP_04_1</t>
+  </si>
+  <si>
+    <t>PP_04_2</t>
+  </si>
+  <si>
+    <t>PP_05_1</t>
+  </si>
+  <si>
+    <t>PP_05_2</t>
+  </si>
+  <si>
+    <t>PP_06_1</t>
+  </si>
+  <si>
+    <t>PP_06_2</t>
+  </si>
+  <si>
+    <t>PP_07_1</t>
+  </si>
+  <si>
+    <t>PP_07_2</t>
+  </si>
+  <si>
+    <t>PP_08_1</t>
+  </si>
+  <si>
+    <t>PP_08_2</t>
+  </si>
+  <si>
+    <t>PP_09_1</t>
+  </si>
+  <si>
+    <t>PP_09_2</t>
+  </si>
+  <si>
+    <t>PP_10_1</t>
+  </si>
+  <si>
+    <t>PP_10_2</t>
+  </si>
+  <si>
+    <t>PP_11_1</t>
+  </si>
+  <si>
+    <t>PP_11_2</t>
+  </si>
+  <si>
+    <t>PP_12_1</t>
+  </si>
+  <si>
+    <t>PP_12_2</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -1185,10 +1257,10 @@
     </row>
     <row r="5" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="AD5" s="8"/>
       <c r="AG5" s="8"/>
@@ -1200,7 +1272,7 @@
     <row r="6" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="24"/>
       <c r="AC6" s="9" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="AD6" s="10"/>
       <c r="AG6" s="10"/>
@@ -1212,7 +1284,7 @@
     <row r="7" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="24"/>
       <c r="AC7" s="9" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="AD7" s="10"/>
       <c r="AG7" s="10"/>
@@ -1224,7 +1296,7 @@
     <row r="8" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="24"/>
       <c r="AC8" s="9" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="AD8" s="10"/>
       <c r="AG8" s="10"/>
@@ -1236,7 +1308,7 @@
     <row r="9" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="24"/>
       <c r="AC9" s="9" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="AD9" s="10"/>
       <c r="AG9" s="10"/>
@@ -1248,7 +1320,7 @@
     <row r="10" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="24"/>
       <c r="AC10" s="9" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="AD10" s="10"/>
       <c r="AG10" s="10"/>
@@ -1260,7 +1332,7 @@
     <row r="11" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="24"/>
       <c r="AC11" s="9" t="s">
-        <v>139</v>
+        <v>115</v>
       </c>
       <c r="AD11" s="10"/>
       <c r="AG11" s="10"/>
@@ -1272,7 +1344,7 @@
     <row r="12" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="24"/>
       <c r="AC12" s="9" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="AD12" s="10"/>
       <c r="AG12" s="10"/>
@@ -1284,7 +1356,7 @@
     <row r="13" spans="1:45" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="24"/>
       <c r="AC13" s="9" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="AD13" s="10"/>
       <c r="AG13" s="10"/>
@@ -1296,7 +1368,7 @@
     <row r="14" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="24"/>
       <c r="AC14" s="9" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="AD14" s="10"/>
       <c r="AG14" s="10"/>
@@ -1308,7 +1380,7 @@
     <row r="15" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="24"/>
       <c r="AC15" s="9" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="AD15" s="10"/>
       <c r="AG15" s="10"/>
@@ -1320,7 +1392,7 @@
     <row r="16" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="24"/>
       <c r="AC16" s="9" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="AD16" s="10"/>
       <c r="AG16" s="10"/>
@@ -1332,7 +1404,7 @@
     <row r="17" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="24"/>
       <c r="AC17" s="9" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="AD17" s="10"/>
       <c r="AG17" s="10"/>
@@ -1344,7 +1416,7 @@
     <row r="18" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="24"/>
       <c r="AC18" s="9" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="AD18" s="10"/>
       <c r="AG18" s="10"/>
@@ -1356,7 +1428,7 @@
     <row r="19" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="24"/>
       <c r="AC19" s="9" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="AD19" s="10"/>
       <c r="AG19" s="10"/>
@@ -1368,7 +1440,7 @@
     <row r="20" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="24"/>
       <c r="AC20" s="9" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="AD20" s="10"/>
       <c r="AG20" s="10"/>
@@ -1379,10 +1451,10 @@
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="AC21" s="9" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="AD21" s="10"/>
       <c r="AG21" s="10"/>
@@ -1394,7 +1466,7 @@
     <row r="22" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="24"/>
       <c r="AC22" s="9" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="AD22" s="10"/>
       <c r="AG22" s="10"/>
@@ -1406,7 +1478,7 @@
     <row r="23" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="24"/>
       <c r="AC23" s="9" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="AD23" s="10"/>
       <c r="AG23" s="10"/>
@@ -1418,7 +1490,7 @@
     <row r="24" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="24"/>
       <c r="AC24" s="11" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="AD24" s="12"/>
       <c r="AG24" s="12"/>
@@ -1430,7 +1502,7 @@
     <row r="25" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="24"/>
       <c r="AC25" s="7" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="AD25" s="8"/>
       <c r="AG25" s="8"/>
@@ -1442,7 +1514,7 @@
     <row r="26" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="24"/>
       <c r="AC26" s="9" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="AD26" s="10"/>
       <c r="AG26" s="10"/>
@@ -1454,7 +1526,7 @@
     <row r="27" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="24"/>
       <c r="AC27" s="9" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="AD27" s="10"/>
       <c r="AG27" s="10"/>
@@ -1466,7 +1538,7 @@
     <row r="28" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="24"/>
       <c r="AC28" s="9" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="AD28" s="10"/>
       <c r="AG28" s="10"/>
@@ -1478,7 +1550,7 @@
     <row r="29" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="24"/>
       <c r="AC29" s="9" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="AD29" s="10"/>
       <c r="AG29" s="10"/>
@@ -1490,7 +1562,7 @@
     <row r="30" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="24"/>
       <c r="AC30" s="9" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="AD30" s="10"/>
       <c r="AG30" s="10"/>
@@ -1502,7 +1574,7 @@
     <row r="31" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="24"/>
       <c r="AC31" s="9" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="AD31" s="10"/>
       <c r="AG31" s="10"/>
@@ -1514,7 +1586,7 @@
     <row r="32" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="24"/>
       <c r="AC32" s="9" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="AD32" s="10"/>
       <c r="AG32" s="10"/>
@@ -1526,7 +1598,7 @@
     <row r="33" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="24"/>
       <c r="AC33" s="9" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
       <c r="AD33" s="10"/>
       <c r="AG33" s="10"/>
@@ -1538,7 +1610,7 @@
     <row r="34" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="24"/>
       <c r="AC34" s="9" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="AD34" s="10"/>
       <c r="AG34" s="10"/>
@@ -1550,7 +1622,7 @@
     <row r="35" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="24"/>
       <c r="AC35" s="9" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="AD35" s="10"/>
       <c r="AG35" s="10"/>
@@ -1562,7 +1634,7 @@
     <row r="36" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="24"/>
       <c r="AC36" s="11" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="AD36" s="12"/>
       <c r="AG36" s="12"/>
@@ -1596,7 +1668,7 @@
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC39" s="7" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="AD39" s="8"/>
       <c r="AG39" s="8"/>
@@ -1607,7 +1679,7 @@
     </row>
     <row r="40" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC40" s="9" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="AD40" s="10"/>
       <c r="AG40" s="10"/>
@@ -1618,7 +1690,7 @@
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="AD41" s="10"/>
       <c r="AG41" s="10"/>
@@ -1629,7 +1701,7 @@
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC42" s="9" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="AD42" s="10"/>
       <c r="AG42" s="10"/>
@@ -1640,7 +1712,7 @@
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC43" s="9" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="AD43" s="10"/>
       <c r="AG43" s="10"/>
@@ -1651,7 +1723,7 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="AD44" s="10"/>
       <c r="AG44" s="10"/>
@@ -1662,7 +1734,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="AD45" s="10"/>
       <c r="AG45" s="10"/>
@@ -1673,7 +1745,7 @@
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC46" s="9" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="AD46" s="10"/>
       <c r="AG46" s="10"/>
@@ -1684,7 +1756,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC47" s="9" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="AD47" s="10"/>
       <c r="AG47" s="10"/>
@@ -1695,7 +1767,7 @@
     </row>
     <row r="48" spans="1:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC48" s="11" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="AD48" s="12"/>
       <c r="AG48" s="12"/>
@@ -1708,7 +1780,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="1J2cDk63Umr0HBBFB3mcMiIbbNXbeKf3TFPTwBtI0JJCmNhayq79KC+79ROGlTowjTQQa80exvwi3r59I3J3MQ==" saltValue="SG3J2yvpvwZWCrpyUTvlOw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -1774,7 +1846,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -1785,7 +1857,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -1979,7 +2051,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -2174,7 +2246,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas DG'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -2472,7 +2544,7 @@
     </row>
     <row r="64" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="INetjJZjJf24HnHpzIv8W9mpR8VfVSUNKIA4QuN6LoXwwSQkiaHacSKHOrupKeTUxMyeCUnd6D3XmCzQcjWcGg==" saltValue="71kHFML3FQZfN/Hl6ioaQw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -2538,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -2549,7 +2621,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -2743,7 +2815,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -2938,7 +3010,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -3236,7 +3308,7 @@
     </row>
     <row r="64" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+mQxza9Wp3g6U8YISAvfazW79LwEi3cBb7iDssIwVBag/ECl6GDuNW7emvJMfBAziSf7q86+TzhCI8s3TDRT9Q==" saltValue="hRIpu6dqldriMXfqAJgKCQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -3301,7 +3373,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -3312,7 +3384,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -3506,7 +3578,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -3701,7 +3773,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -3846,7 +3918,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="kl5FXaR4QE2lOSA8h8WkH4h4zLH1QH3/abfnprYXtfC170ag7NtuwYYykb/o6tWKCPHzLnPzVJVxVoxkUzw3Mw==" saltValue="f7sdpnT901ndWLN8uAP93A==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -3912,7 +3984,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -3923,7 +3995,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -4117,7 +4189,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -4312,7 +4384,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -4357,7 +4429,7 @@
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="AD41" s="10"/>
       <c r="AG41" s="10"/>
@@ -4368,7 +4440,7 @@
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC42" s="9" t="s">
-        <v>63</v>
+        <v>143</v>
       </c>
       <c r="AD42" s="10"/>
       <c r="AG42" s="10"/>
@@ -4379,7 +4451,7 @@
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC43" s="9" t="s">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="AD43" s="10"/>
       <c r="AG43" s="10"/>
@@ -4390,7 +4462,7 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>65</v>
+        <v>145</v>
       </c>
       <c r="AD44" s="10"/>
       <c r="AG44" s="10"/>
@@ -4401,7 +4473,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="AD45" s="10"/>
       <c r="AG45" s="10"/>
@@ -4412,7 +4484,7 @@
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC46" s="9" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="AD46" s="10"/>
       <c r="AG46" s="10"/>
@@ -4423,7 +4495,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC47" s="9" t="s">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="AD47" s="10"/>
       <c r="AG47" s="10"/>
@@ -4434,7 +4506,7 @@
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC48" s="9" t="s">
-        <v>69</v>
+        <v>149</v>
       </c>
       <c r="AD48" s="10"/>
       <c r="AG48" s="10"/>
@@ -4445,7 +4517,7 @@
     </row>
     <row r="49" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC49" s="9" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AD49" s="10"/>
       <c r="AG49" s="10"/>
@@ -4456,7 +4528,7 @@
     </row>
     <row r="50" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC50" s="9" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="AD50" s="10"/>
       <c r="AG50" s="10"/>
@@ -4467,7 +4539,7 @@
     </row>
     <row r="51" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC51" s="9" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="AD51" s="10"/>
       <c r="AG51" s="10"/>
@@ -4478,7 +4550,7 @@
     </row>
     <row r="52" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC52" s="9" t="s">
-        <v>73</v>
+        <v>153</v>
       </c>
       <c r="AD52" s="10"/>
       <c r="AG52" s="10"/>
@@ -4489,7 +4561,7 @@
     </row>
     <row r="53" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC53" s="9" t="s">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="AD53" s="10"/>
       <c r="AG53" s="10"/>
@@ -4500,7 +4572,7 @@
     </row>
     <row r="54" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC54" s="9" t="s">
-        <v>75</v>
+        <v>155</v>
       </c>
       <c r="AD54" s="10"/>
       <c r="AG54" s="10"/>
@@ -4511,7 +4583,7 @@
     </row>
     <row r="55" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC55" s="9" t="s">
-        <v>76</v>
+        <v>156</v>
       </c>
       <c r="AD55" s="10"/>
       <c r="AG55" s="10"/>
@@ -4522,7 +4594,7 @@
     </row>
     <row r="56" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC56" s="9" t="s">
-        <v>77</v>
+        <v>157</v>
       </c>
       <c r="AD56" s="10"/>
       <c r="AG56" s="10"/>
@@ -4533,7 +4605,7 @@
     </row>
     <row r="57" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC57" s="9" t="s">
-        <v>61</v>
+        <v>158</v>
       </c>
       <c r="AD57" s="10"/>
       <c r="AG57" s="10"/>
@@ -4544,7 +4616,7 @@
     </row>
     <row r="58" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC58" s="9" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="AD58" s="10"/>
       <c r="AG58" s="10"/>
@@ -4555,7 +4627,7 @@
     </row>
     <row r="59" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC59" s="9" t="s">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="AD59" s="10"/>
       <c r="AG59" s="10"/>
@@ -4566,7 +4638,7 @@
     </row>
     <row r="60" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC60" s="9" t="s">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="AD60" s="10"/>
       <c r="AG60" s="10"/>
@@ -4577,7 +4649,7 @@
     </row>
     <row r="61" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC61" s="9" t="s">
-        <v>81</v>
+        <v>162</v>
       </c>
       <c r="AD61" s="10"/>
       <c r="AG61" s="10"/>
@@ -4588,7 +4660,7 @@
     </row>
     <row r="62" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC62" s="9" t="s">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="AD62" s="10"/>
       <c r="AG62" s="10"/>
@@ -4599,7 +4671,7 @@
     </row>
     <row r="63" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC63" s="9" t="s">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="AD63" s="10"/>
       <c r="AG63" s="10"/>
@@ -4610,7 +4682,7 @@
     </row>
     <row r="64" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC64" s="13" t="s">
-        <v>84</v>
+        <v>165</v>
       </c>
       <c r="AD64" s="20"/>
       <c r="AG64" s="20"/>
@@ -4676,7 +4748,7 @@
     </row>
     <row r="70" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="tAZ6UCeLSW4DUrSeHGdEb12uNpcFxUP2PjcIQkUyGWwJZ4VbPHk3i5qr9WYbnpkXO0uXiB8ee8uLj7wKxdqKFw==" saltValue="g5kttvYrX/uTE9ctJRRVrw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -4741,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -4752,7 +4824,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -4946,7 +5018,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -5141,7 +5213,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -5164,7 +5236,7 @@
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC39" s="7" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="AD39" s="8"/>
       <c r="AG39" s="8"/>
@@ -5219,7 +5291,7 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="AD44" s="10"/>
       <c r="AG44" s="10"/>
@@ -5252,7 +5324,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC47" s="9" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="AD47" s="10"/>
       <c r="AG47" s="10"/>
@@ -5285,7 +5357,7 @@
     </row>
     <row r="50" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC50" s="9" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="AD50" s="10"/>
       <c r="AG50" s="10"/>
@@ -5318,7 +5390,7 @@
     </row>
     <row r="53" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC53" s="9" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AD53" s="10"/>
       <c r="AG53" s="10"/>
@@ -5351,7 +5423,7 @@
     </row>
     <row r="56" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC56" s="9" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="AD56" s="10"/>
       <c r="AG56" s="10"/>
@@ -5384,7 +5456,7 @@
     </row>
     <row r="59" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC59" s="9" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AD59" s="10"/>
       <c r="AG59" s="10"/>
@@ -5395,7 +5467,7 @@
     </row>
     <row r="60" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC60" s="9" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AD60" s="10"/>
       <c r="AG60" s="10"/>
@@ -5406,7 +5478,7 @@
     </row>
     <row r="61" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC61" s="9" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="AD61" s="10"/>
       <c r="AG61" s="10"/>
@@ -5417,7 +5489,7 @@
     </row>
     <row r="62" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC62" s="9" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="AD62" s="10"/>
       <c r="AG62" s="10"/>
@@ -5428,7 +5500,7 @@
     </row>
     <row r="63" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC63" s="9" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="AD63" s="10"/>
       <c r="AG63" s="10"/>
@@ -5439,7 +5511,7 @@
     </row>
     <row r="64" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC64" s="9" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="AD64" s="10"/>
       <c r="AG64" s="10"/>
@@ -5450,7 +5522,7 @@
     </row>
     <row r="65" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC65" s="13" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AD65" s="20"/>
       <c r="AG65" s="20"/>
@@ -5524,7 +5596,7 @@
       <c r="AS71"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mw+DdyguqclqTK4ArGaRpvtQkIcL5yk7lagquQQ3+nHmxBy5qbhjQS2G3cTXMtCWIa9ralfBpCigUJN6Op+F0g==" saltValue="NjRi0jRoEIPtsgMmXEtXBQ==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -5589,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -5600,7 +5672,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -5794,7 +5866,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -5989,7 +6061,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -6034,7 +6106,7 @@
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="AD41" s="10"/>
       <c r="AG41" s="10"/>
@@ -6045,7 +6117,7 @@
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC42" s="9" t="s">
-        <v>63</v>
+        <v>168</v>
       </c>
       <c r="AD42" s="10"/>
       <c r="AG42" s="10"/>
@@ -6056,7 +6128,7 @@
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC43" s="9" t="s">
-        <v>64</v>
+        <v>169</v>
       </c>
       <c r="AD43" s="10"/>
       <c r="AG43" s="10"/>
@@ -6067,7 +6139,7 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AD44" s="10"/>
       <c r="AG44" s="10"/>
@@ -6078,7 +6150,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
       <c r="AD45" s="10"/>
       <c r="AG45" s="10"/>
@@ -6089,7 +6161,7 @@
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC46" s="9" t="s">
-        <v>67</v>
+        <v>172</v>
       </c>
       <c r="AD46" s="10"/>
       <c r="AG46" s="10"/>
@@ -6100,7 +6172,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC47" s="9" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="AD47" s="10"/>
       <c r="AG47" s="10"/>
@@ -6111,7 +6183,7 @@
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC48" s="9" t="s">
-        <v>69</v>
+        <v>174</v>
       </c>
       <c r="AD48" s="10"/>
       <c r="AG48" s="10"/>
@@ -6122,7 +6194,7 @@
     </row>
     <row r="49" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC49" s="9" t="s">
-        <v>70</v>
+        <v>175</v>
       </c>
       <c r="AD49" s="10"/>
       <c r="AG49" s="10"/>
@@ -6133,7 +6205,7 @@
     </row>
     <row r="50" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC50" s="9" t="s">
-        <v>71</v>
+        <v>176</v>
       </c>
       <c r="AD50" s="10"/>
       <c r="AG50" s="10"/>
@@ -6144,7 +6216,7 @@
     </row>
     <row r="51" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC51" s="9" t="s">
-        <v>72</v>
+        <v>177</v>
       </c>
       <c r="AD51" s="10"/>
       <c r="AG51" s="10"/>
@@ -6155,7 +6227,7 @@
     </row>
     <row r="52" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC52" s="9" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AD52" s="10"/>
       <c r="AG52" s="10"/>
@@ -6166,7 +6238,7 @@
     </row>
     <row r="53" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC53" s="9" t="s">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="AD53" s="10"/>
       <c r="AG53" s="10"/>
@@ -6177,7 +6249,7 @@
     </row>
     <row r="54" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC54" s="9" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="AD54" s="10"/>
       <c r="AG54" s="10"/>
@@ -6188,7 +6260,7 @@
     </row>
     <row r="55" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC55" s="9" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="AD55" s="10"/>
       <c r="AG55" s="10"/>
@@ -6199,7 +6271,7 @@
     </row>
     <row r="56" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC56" s="9" t="s">
-        <v>77</v>
+        <v>182</v>
       </c>
       <c r="AD56" s="10"/>
       <c r="AG56" s="10"/>
@@ -6210,7 +6282,7 @@
     </row>
     <row r="57" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC57" s="9" t="s">
-        <v>61</v>
+        <v>183</v>
       </c>
       <c r="AD57" s="10"/>
       <c r="AG57" s="10"/>
@@ -6221,7 +6293,7 @@
     </row>
     <row r="58" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC58" s="9" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AD58" s="10"/>
       <c r="AG58" s="10"/>
@@ -6232,7 +6304,7 @@
     </row>
     <row r="59" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC59" s="9" t="s">
-        <v>79</v>
+        <v>185</v>
       </c>
       <c r="AD59" s="10"/>
       <c r="AG59" s="10"/>
@@ -6243,7 +6315,7 @@
     </row>
     <row r="60" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC60" s="9" t="s">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="AD60" s="10"/>
       <c r="AG60" s="10"/>
@@ -6254,7 +6326,7 @@
     </row>
     <row r="61" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC61" s="9" t="s">
-        <v>81</v>
+        <v>187</v>
       </c>
       <c r="AD61" s="10"/>
       <c r="AG61" s="10"/>
@@ -6265,7 +6337,7 @@
     </row>
     <row r="62" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC62" s="9" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="AD62" s="10"/>
       <c r="AG62" s="10"/>
@@ -6276,7 +6348,7 @@
     </row>
     <row r="63" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC63" s="9" t="s">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="AD63" s="10"/>
       <c r="AG63" s="10"/>
@@ -6287,7 +6359,7 @@
     </row>
     <row r="64" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC64" s="13" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
       <c r="AD64" s="20"/>
       <c r="AG64" s="20"/>
@@ -6360,7 +6432,7 @@
       <c r="AS70" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="y76TPVc7MNSb8nK/+cTeoe9+D7sWbrSXC4t9wjWj7hS8K4L6Qir3iWAOzgmhxqp1beTdCiBhvQyVDyIiKlgQbw==" saltValue="hXPhg094EVz5P35Wwhq+CA==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -6425,7 +6497,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -6436,7 +6508,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -6630,7 +6702,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -6825,7 +6897,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -6870,7 +6942,7 @@
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="AD41" s="10"/>
       <c r="AG41" s="10"/>
@@ -6881,7 +6953,7 @@
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC42" s="9" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="AD42" s="10"/>
       <c r="AG42" s="10"/>
@@ -6892,7 +6964,7 @@
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC43" s="9" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="AD43" s="10"/>
       <c r="AG43" s="10"/>
@@ -6903,7 +6975,7 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="AD44" s="10"/>
       <c r="AG44" s="10"/>
@@ -6914,7 +6986,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="AD45" s="10"/>
       <c r="AG45" s="10"/>
@@ -6925,7 +6997,7 @@
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC46" s="9" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="AD46" s="10"/>
       <c r="AG46" s="10"/>
@@ -6936,7 +7008,7 @@
     </row>
     <row r="47" spans="1:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC47" s="11" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="AD47" s="12"/>
       <c r="AE47" s="17"/>
@@ -6970,7 +7042,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mGHJbEDqrvHZcdgX6Qajq7Q3PE6ZwqFjhWYfdKs/SKInvoil8mjXopB9WXs96Gam//4mRmUi3AxrugiicgbzUw==" saltValue="tiFaoNTJ4E+hnks3i0vW2Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -7035,7 +7107,7 @@
         <v>0</v>
       </c>
       <c r="AC4" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="AD4" s="4"/>
       <c r="AG4" s="4"/>
@@ -7046,7 +7118,7 @@
     </row>
     <row r="5" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="24" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="AC5" s="7" t="s">
         <v>0</v>
@@ -7240,7 +7312,7 @@
     </row>
     <row r="21" spans="1:45" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="24" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="AC21" s="9" t="s">
         <v>16</v>
@@ -7435,7 +7507,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.0</v>
+        <v>V - 8.3</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -7546,7 +7618,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="6YlU1uZ98Mtx2qqrzEd6gxDm96w0IbLAIQ22JJZbuQfwBy+Gs6/FoGfO+GEG09PVlDeah46Si2dc3avBljOhGg==" saltValue="3lzqRZJ6Z3J8SLBCc/YB8w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>

--- a/FastTest PlugIn - Formula.xlsx
+++ b/FastTest PlugIn - Formula.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28422"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AHGM\0. GITHUB\FTP_Privado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{496915DE-200A-4A5C-AC3A-FEEB73AD1221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC2ED755-8EB3-49B9-AC09-0F5E5CFBD531}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="19386" windowHeight="12986" tabRatio="805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
     <sheet name="Formulas EN" sheetId="5" r:id="rId8"/>
     <sheet name="Formulas CL" sheetId="6" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="193">
   <si>
     <t>DATO_01</t>
   </si>
@@ -544,9 +544,6 @@
     <t>P_12_2</t>
   </si>
   <si>
-    <t>V - 8.3</t>
-  </si>
-  <si>
     <t>PP_01_1</t>
   </si>
   <si>
@@ -617,6 +614,15 @@
   </si>
   <si>
     <t>PP_12_2</t>
+  </si>
+  <si>
+    <t>Nº MAX RESP</t>
+  </si>
+  <si>
+    <t>ANCHO IMG</t>
+  </si>
+  <si>
+    <t>V - 8.5</t>
   </si>
 </sst>
 </file>
@@ -1645,7 +1651,7 @@
     </row>
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -1780,7 +1786,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -2246,7 +2252,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas DG'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -2544,7 +2550,7 @@
     </row>
     <row r="64" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -2557,7 +2563,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AS64"/>
+  <dimension ref="A1:AS65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.35" zeroHeight="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6.64453125" customWidth="1"/>
@@ -3010,7 +3016,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -3251,9 +3257,9 @@
       <c r="AP58" s="20"/>
       <c r="AS58" s="20"/>
     </row>
-    <row r="59" spans="29:45" x14ac:dyDescent="0.5">
+    <row r="59" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC59" s="15" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="AD59" s="21"/>
       <c r="AG59" s="21"/>
@@ -3263,15 +3269,15 @@
       <c r="AS59" s="21"/>
     </row>
     <row r="60" spans="29:45" x14ac:dyDescent="0.5">
-      <c r="AC60" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD60" s="10"/>
-      <c r="AG60" s="10"/>
-      <c r="AJ60" s="10"/>
-      <c r="AM60" s="10"/>
-      <c r="AP60" s="10"/>
-      <c r="AS60" s="10"/>
+      <c r="AC60" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD60" s="21"/>
+      <c r="AG60" s="21"/>
+      <c r="AJ60" s="21"/>
+      <c r="AM60" s="21"/>
+      <c r="AP60" s="21"/>
+      <c r="AS60" s="21"/>
     </row>
     <row r="61" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC61" s="9" t="s">
@@ -3286,7 +3292,7 @@
     </row>
     <row r="62" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC62" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD62" s="10"/>
       <c r="AG62" s="10"/>
@@ -3295,20 +3301,31 @@
       <c r="AP62" s="10"/>
       <c r="AS62" s="10"/>
     </row>
-    <row r="63" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AC63" s="11" t="s">
+    <row r="63" spans="29:45" x14ac:dyDescent="0.5">
+      <c r="AC63" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD63" s="10"/>
+      <c r="AG63" s="10"/>
+      <c r="AJ63" s="10"/>
+      <c r="AM63" s="10"/>
+      <c r="AP63" s="10"/>
+      <c r="AS63" s="10"/>
+    </row>
+    <row r="64" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AC64" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AD63" s="12"/>
-      <c r="AG63" s="12"/>
-      <c r="AJ63" s="12"/>
-      <c r="AM63" s="12"/>
-      <c r="AP63" s="12"/>
-      <c r="AS63" s="12"/>
-    </row>
-    <row r="64" spans="29:45" x14ac:dyDescent="0.5"/>
+      <c r="AD64" s="12"/>
+      <c r="AG64" s="12"/>
+      <c r="AJ64" s="12"/>
+      <c r="AM64" s="12"/>
+      <c r="AP64" s="12"/>
+      <c r="AS64" s="12"/>
+    </row>
+    <row r="65" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -3773,7 +3790,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -3918,7 +3935,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -4384,7 +4401,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -4748,7 +4765,7 @@
     </row>
     <row r="70" spans="29:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -5213,7 +5230,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -5596,7 +5613,7 @@
       <c r="AS71"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -6061,7 +6078,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -6106,7 +6123,7 @@
     </row>
     <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AD41" s="10"/>
       <c r="AG41" s="10"/>
@@ -6117,7 +6134,7 @@
     </row>
     <row r="42" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC42" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AD42" s="10"/>
       <c r="AG42" s="10"/>
@@ -6128,7 +6145,7 @@
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC43" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AD43" s="10"/>
       <c r="AG43" s="10"/>
@@ -6139,7 +6156,7 @@
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="AD44" s="10"/>
       <c r="AG44" s="10"/>
@@ -6150,7 +6167,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AD45" s="10"/>
       <c r="AG45" s="10"/>
@@ -6161,7 +6178,7 @@
     </row>
     <row r="46" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC46" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AD46" s="10"/>
       <c r="AG46" s="10"/>
@@ -6172,7 +6189,7 @@
     </row>
     <row r="47" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC47" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AD47" s="10"/>
       <c r="AG47" s="10"/>
@@ -6183,7 +6200,7 @@
     </row>
     <row r="48" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC48" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AD48" s="10"/>
       <c r="AG48" s="10"/>
@@ -6194,7 +6211,7 @@
     </row>
     <row r="49" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AD49" s="10"/>
       <c r="AG49" s="10"/>
@@ -6205,7 +6222,7 @@
     </row>
     <row r="50" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC50" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AD50" s="10"/>
       <c r="AG50" s="10"/>
@@ -6216,7 +6233,7 @@
     </row>
     <row r="51" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC51" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AD51" s="10"/>
       <c r="AG51" s="10"/>
@@ -6227,7 +6244,7 @@
     </row>
     <row r="52" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC52" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="AD52" s="10"/>
       <c r="AG52" s="10"/>
@@ -6238,7 +6255,7 @@
     </row>
     <row r="53" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC53" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AD53" s="10"/>
       <c r="AG53" s="10"/>
@@ -6249,7 +6266,7 @@
     </row>
     <row r="54" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC54" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AD54" s="10"/>
       <c r="AG54" s="10"/>
@@ -6260,7 +6277,7 @@
     </row>
     <row r="55" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC55" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AD55" s="10"/>
       <c r="AG55" s="10"/>
@@ -6271,7 +6288,7 @@
     </row>
     <row r="56" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC56" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AD56" s="10"/>
       <c r="AG56" s="10"/>
@@ -6282,7 +6299,7 @@
     </row>
     <row r="57" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC57" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AD57" s="10"/>
       <c r="AG57" s="10"/>
@@ -6293,7 +6310,7 @@
     </row>
     <row r="58" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC58" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AD58" s="10"/>
       <c r="AG58" s="10"/>
@@ -6304,7 +6321,7 @@
     </row>
     <row r="59" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC59" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AD59" s="10"/>
       <c r="AG59" s="10"/>
@@ -6315,7 +6332,7 @@
     </row>
     <row r="60" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC60" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AD60" s="10"/>
       <c r="AG60" s="10"/>
@@ -6326,7 +6343,7 @@
     </row>
     <row r="61" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC61" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AD61" s="10"/>
       <c r="AG61" s="10"/>
@@ -6337,7 +6354,7 @@
     </row>
     <row r="62" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC62" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AD62" s="10"/>
       <c r="AG62" s="10"/>
@@ -6348,7 +6365,7 @@
     </row>
     <row r="63" spans="29:45" x14ac:dyDescent="0.5">
       <c r="AC63" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AD63" s="10"/>
       <c r="AG63" s="10"/>
@@ -6359,7 +6376,7 @@
     </row>
     <row r="64" spans="29:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="AC64" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AD64" s="20"/>
       <c r="AG64" s="20"/>
@@ -6432,7 +6449,7 @@
       <c r="AS70" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -6897,7 +6914,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -7042,7 +7059,7 @@
       <c r="AC49" s="1"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
@@ -7054,7 +7071,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr codeName="Hoja8"/>
-  <dimension ref="A1:AS47"/>
+  <dimension ref="A1:AS48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.35" zeroHeight="1" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="6.64453125" customWidth="1"/>
@@ -7507,7 +7524,7 @@
     <row r="37" spans="1:45" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="16" t="str">
         <f>'Formulas OM'!A37</f>
-        <v>V - 8.3</v>
+        <v>V - 8.5</v>
       </c>
       <c r="AC37" s="2"/>
       <c r="AD37" s="2"/>
@@ -7550,7 +7567,7 @@
       <c r="AP40" s="10"/>
       <c r="AS40" s="10"/>
     </row>
-    <row r="41" spans="1:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC41" s="9" t="s">
         <v>34</v>
       </c>
@@ -7561,27 +7578,27 @@
       <c r="AP41" s="10"/>
       <c r="AS41" s="10"/>
     </row>
-    <row r="42" spans="1:45" x14ac:dyDescent="0.5">
-      <c r="AC42" s="15" t="s">
+    <row r="42" spans="1:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AC42" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="AD42" s="10"/>
+      <c r="AG42" s="10"/>
+      <c r="AJ42" s="10"/>
+      <c r="AM42" s="10"/>
+      <c r="AP42" s="10"/>
+      <c r="AS42" s="10"/>
+    </row>
+    <row r="43" spans="1:45" x14ac:dyDescent="0.5">
+      <c r="AC43" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="AD42" s="21"/>
-      <c r="AG42" s="21"/>
-      <c r="AJ42" s="21"/>
-      <c r="AM42" s="21"/>
-      <c r="AP42" s="21"/>
-      <c r="AS42" s="21"/>
-    </row>
-    <row r="43" spans="1:45" x14ac:dyDescent="0.5">
-      <c r="AC43" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD43" s="10"/>
-      <c r="AG43" s="10"/>
-      <c r="AJ43" s="10"/>
-      <c r="AM43" s="10"/>
-      <c r="AP43" s="10"/>
-      <c r="AS43" s="10"/>
+      <c r="AD43" s="21"/>
+      <c r="AG43" s="21"/>
+      <c r="AJ43" s="21"/>
+      <c r="AM43" s="21"/>
+      <c r="AP43" s="21"/>
+      <c r="AS43" s="21"/>
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC44" s="9" t="s">
@@ -7596,7 +7613,7 @@
     </row>
     <row r="45" spans="1:45" x14ac:dyDescent="0.5">
       <c r="AC45" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AD45" s="10"/>
       <c r="AG45" s="10"/>
@@ -7605,20 +7622,31 @@
       <c r="AP45" s="10"/>
       <c r="AS45" s="10"/>
     </row>
-    <row r="46" spans="1:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="AC46" s="11" t="s">
+    <row r="46" spans="1:45" x14ac:dyDescent="0.5">
+      <c r="AC46" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD46" s="10"/>
+      <c r="AG46" s="10"/>
+      <c r="AJ46" s="10"/>
+      <c r="AM46" s="10"/>
+      <c r="AP46" s="10"/>
+      <c r="AS46" s="10"/>
+    </row>
+    <row r="47" spans="1:45" ht="14.7" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="AC47" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AD46" s="12"/>
-      <c r="AG46" s="12"/>
-      <c r="AJ46" s="12"/>
-      <c r="AM46" s="12"/>
-      <c r="AP46" s="12"/>
-      <c r="AS46" s="12"/>
-    </row>
-    <row r="47" spans="1:45" x14ac:dyDescent="0.5"/>
+      <c r="AD47" s="12"/>
+      <c r="AG47" s="12"/>
+      <c r="AJ47" s="12"/>
+      <c r="AM47" s="12"/>
+      <c r="AP47" s="12"/>
+      <c r="AS47" s="12"/>
+    </row>
+    <row r="48" spans="1:45" x14ac:dyDescent="0.5"/>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" autoFilter="0"/>
+  <sheetProtection selectLockedCells="1" autoFilter="0"/>
   <mergeCells count="2">
     <mergeCell ref="A5:A20"/>
     <mergeCell ref="A21:A36"/>
